--- a/RL/results_film_b_multibudget.xlsx
+++ b/RL/results_film_b_multibudget.xlsx
@@ -566,49 +566,49 @@
         <v>146.71</v>
       </c>
       <c r="H2" t="n">
-        <v>15267</v>
+        <v>14818</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>181.29</v>
+        <v>147.91</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.68</v>
+        <v>1.31</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>15015</v>
+        <v>14818</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>146.71</v>
+        <v>147.91</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>252.1</v>
+        <v>182.8</v>
       </c>
       <c r="V2" t="n">
-        <v>93.29000000000001</v>
+        <v>92.09</v>
       </c>
     </row>
     <row r="3">
@@ -636,49 +636,49 @@
         <v>7.19</v>
       </c>
       <c r="H3" t="n">
-        <v>21006</v>
+        <v>17074</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>7.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>18.72</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>21006</v>
+        <v>17074</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>7.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>18.72</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>137.4</v>
+        <v>142.3</v>
       </c>
       <c r="V3" t="n">
-        <v>232.81</v>
+        <v>231.61</v>
       </c>
     </row>
     <row r="4">
@@ -745,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>36.7</v>
+        <v>34.8</v>
       </c>
       <c r="V4" t="n">
         <v>200.63</v>
@@ -776,49 +776,49 @@
         <v>39.37</v>
       </c>
       <c r="H5" t="n">
-        <v>12006</v>
+        <v>8074</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>32.75</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>12006</v>
+        <v>8074</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>32.75</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>91.7</v>
+        <v>99.7</v>
       </c>
       <c r="V5" t="n">
-        <v>200.63</v>
+        <v>199.43</v>
       </c>
     </row>
     <row r="6">
@@ -846,49 +846,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3509</v>
+        <v>3312</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3509</v>
+        <v>3312</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>31.8</v>
+        <v>35.2</v>
       </c>
       <c r="V6" t="n">
-        <v>164.85</v>
+        <v>163.65</v>
       </c>
     </row>
     <row r="7">
@@ -916,49 +916,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>6010</v>
+        <v>5813</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6010</v>
+        <v>5813</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>47.2</v>
+        <v>55.5</v>
       </c>
       <c r="V7" t="n">
-        <v>163.65</v>
+        <v>162.45</v>
       </c>
     </row>
     <row r="8">
@@ -986,49 +986,49 @@
         <v>77.55</v>
       </c>
       <c r="H8" t="n">
-        <v>20013</v>
+        <v>19564</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>112.13</v>
+        <v>78.75</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.28</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>19761</v>
+        <v>19564</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>77.55</v>
+        <v>78.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>158.2</v>
+        <v>158.8</v>
       </c>
       <c r="V8" t="n">
-        <v>162.45</v>
+        <v>161.25</v>
       </c>
     </row>
     <row r="9">
@@ -1095,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>47.6</v>
+        <v>49</v>
       </c>
       <c r="V9" t="n">
         <v>164.85</v>
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>161.3</v>
+        <v>136.6</v>
       </c>
       <c r="V10" t="n">
         <v>164.85</v>
@@ -1196,49 +1196,49 @@
         <v>40.57</v>
       </c>
       <c r="H11" t="n">
-        <v>2757</v>
+        <v>2560</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2757</v>
+        <v>2560</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>29.3</v>
+        <v>32.6</v>
       </c>
       <c r="V11" t="n">
-        <v>199.43</v>
+        <v>198.23</v>
       </c>
     </row>
     <row r="12">
@@ -1266,49 +1266,49 @@
         <v>41.77</v>
       </c>
       <c r="H12" t="n">
-        <v>4758</v>
+        <v>4561</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4758</v>
+        <v>4561</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>45.2</v>
+        <v>47.7</v>
       </c>
       <c r="V12" t="n">
-        <v>198.23</v>
+        <v>197.03</v>
       </c>
     </row>
     <row r="13">
@@ -1336,49 +1336,49 @@
         <v>42.97</v>
       </c>
       <c r="H13" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>120</v>
+        <v>147.1</v>
       </c>
       <c r="V13" t="n">
-        <v>197.03</v>
+        <v>195.84</v>
       </c>
     </row>
     <row r="14">
@@ -1406,49 +1406,49 @@
         <v>39.37</v>
       </c>
       <c r="H14" t="n">
-        <v>1256</v>
+        <v>1059</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1256</v>
+        <v>1059</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="V14" t="n">
-        <v>200.63</v>
+        <v>199.43</v>
       </c>
     </row>
     <row r="15">
@@ -1476,49 +1476,49 @@
         <v>40.57</v>
       </c>
       <c r="H15" t="n">
-        <v>2257</v>
+        <v>2060</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2257</v>
+        <v>2060</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
       <c r="R15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>39.4</v>
+        <v>32.1</v>
       </c>
       <c r="V15" t="n">
-        <v>199.43</v>
+        <v>198.23</v>
       </c>
     </row>
     <row r="16">
@@ -1546,49 +1546,49 @@
         <v>41.77</v>
       </c>
       <c r="H16" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>78.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="V16" t="n">
-        <v>198.23</v>
+        <v>197.03</v>
       </c>
     </row>
     <row r="17">
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="V17" t="n">
         <v>199.43</v>
@@ -1725,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>166.9</v>
+        <v>173.6</v>
       </c>
       <c r="V18" t="n">
         <v>199.43</v>
@@ -1756,49 +1756,49 @@
         <v>39.37</v>
       </c>
       <c r="H19" t="n">
-        <v>28006</v>
+        <v>24074</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>14.04</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>28006</v>
+        <v>24074</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>14.04</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>102.8</v>
+        <v>151.8</v>
       </c>
       <c r="V19" t="n">
-        <v>200.63</v>
+        <v>199.43</v>
       </c>
     </row>
     <row r="20">
@@ -1826,49 +1826,49 @@
         <v>110.93</v>
       </c>
       <c r="H20" t="n">
-        <v>7012</v>
+        <v>6815</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7012</v>
+        <v>6815</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>51.5</v>
+        <v>65.5</v>
       </c>
       <c r="V20" t="n">
-        <v>129.07</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="21">
@@ -1896,49 +1896,49 @@
         <v>218.27</v>
       </c>
       <c r="H21" t="n">
-        <v>29273</v>
+        <v>28824</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>252.85</v>
+        <v>219.47</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.87</v>
+        <v>0.68</v>
       </c>
       <c r="L21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>29021</v>
+        <v>28824</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>218.27</v>
+        <v>219.47</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>144</v>
+        <v>161.4</v>
       </c>
       <c r="V21" t="n">
-        <v>21.73</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="22">
@@ -1966,49 +1966,49 @@
         <v>182.49</v>
       </c>
       <c r="H22" t="n">
-        <v>8269</v>
+        <v>7920</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>215.87</v>
+        <v>183.69</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.13</v>
+        <v>1.22</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>8018</v>
+        <v>7920</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>182.49</v>
+        <v>183.69</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>64.7</v>
+        <v>62.1</v>
       </c>
       <c r="V22" t="n">
-        <v>57.51</v>
+        <v>56.31</v>
       </c>
     </row>
     <row r="23">
@@ -2036,49 +2036,49 @@
         <v>141.92</v>
       </c>
       <c r="H23" t="n">
-        <v>7761</v>
+        <v>7663</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>141.92</v>
+        <v>143.12</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>7761</v>
+        <v>7663</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>141.92</v>
+        <v>143.12</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>80.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>98.08</v>
+        <v>96.88</v>
       </c>
     </row>
     <row r="24">
@@ -2106,7 +2106,7 @@
         <v>7.19</v>
       </c>
       <c r="H24" t="n">
-        <v>10006</v>
+        <v>7757</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2115,13 +2115,13 @@
         <v>7.19</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>22.48</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>10006</v>
+        <v>7757</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2130,22 +2130,22 @@
         <v>7.19</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>22.48</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>100.3</v>
+        <v>78.8</v>
       </c>
       <c r="V24" t="n">
         <v>232.81</v>
@@ -2215,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>398.2</v>
+        <v>152.9</v>
       </c>
       <c r="V25" t="n">
         <v>232.81</v>
@@ -2285,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>69.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="V26" t="n">
         <v>200.63</v>
@@ -2355,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>116.6</v>
+        <v>113.4</v>
       </c>
       <c r="V27" t="n">
         <v>200.63</v>
@@ -2386,49 +2386,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>4759</v>
+        <v>4562</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4759</v>
+        <v>4562</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>52.1</v>
+        <v>62.9</v>
       </c>
       <c r="V28" t="n">
-        <v>164.85</v>
+        <v>163.65</v>
       </c>
     </row>
     <row r="29">
@@ -2456,49 +2456,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
       <c r="V29" t="n">
-        <v>163.65</v>
+        <v>162.45</v>
       </c>
     </row>
     <row r="30">
@@ -2526,49 +2526,49 @@
         <v>78.75</v>
       </c>
       <c r="H30" t="n">
-        <v>39762</v>
+        <v>39565</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>78.75</v>
+        <v>79.94</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>39762</v>
+        <v>39565</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>78.75</v>
+        <v>79.94</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>188.5</v>
+        <v>428.8</v>
       </c>
       <c r="V30" t="n">
-        <v>161.25</v>
+        <v>160.06</v>
       </c>
     </row>
     <row r="31">
@@ -2596,49 +2596,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>10009</v>
+        <v>8069</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>19.38</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>10009</v>
+        <v>8069</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>19.38</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>95.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="V31" t="n">
-        <v>164.85</v>
+        <v>163.65</v>
       </c>
     </row>
     <row r="32">
@@ -2705,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>148.5</v>
+        <v>157.1</v>
       </c>
       <c r="V32" t="n">
         <v>164.85</v>
@@ -2736,49 +2736,49 @@
         <v>40.57</v>
       </c>
       <c r="H33" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>38.5</v>
+        <v>42.4</v>
       </c>
       <c r="V33" t="n">
-        <v>199.43</v>
+        <v>198.23</v>
       </c>
     </row>
     <row r="34">
@@ -2806,49 +2806,49 @@
         <v>41.77</v>
       </c>
       <c r="H34" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>72.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V34" t="n">
-        <v>198.23</v>
+        <v>197.03</v>
       </c>
     </row>
     <row r="35">
@@ -2876,49 +2876,49 @@
         <v>44.16</v>
       </c>
       <c r="H35" t="n">
-        <v>31760</v>
+        <v>31563</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>44.16</v>
+        <v>45.36</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>31760</v>
+        <v>31563</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>44.16</v>
+        <v>45.36</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>139.6</v>
+        <v>136.1</v>
       </c>
       <c r="V35" t="n">
-        <v>195.84</v>
+        <v>194.64</v>
       </c>
     </row>
     <row r="36">
@@ -2946,49 +2946,49 @@
         <v>39.37</v>
       </c>
       <c r="H36" t="n">
-        <v>1756</v>
+        <v>1559</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>11.22</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1756</v>
+        <v>1559</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>11.22</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="V36" t="n">
-        <v>200.63</v>
+        <v>199.43</v>
       </c>
     </row>
     <row r="37">
@@ -3016,49 +3016,49 @@
         <v>40.57</v>
       </c>
       <c r="H37" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>50.1</v>
+        <v>44</v>
       </c>
       <c r="V37" t="n">
-        <v>199.43</v>
+        <v>198.23</v>
       </c>
     </row>
     <row r="38">
@@ -3086,49 +3086,49 @@
         <v>42.97</v>
       </c>
       <c r="H38" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>89.7</v>
+        <v>139.1</v>
       </c>
       <c r="V38" t="n">
-        <v>197.03</v>
+        <v>195.84</v>
       </c>
     </row>
     <row r="39">
@@ -3195,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>132.8</v>
+        <v>233.1</v>
       </c>
       <c r="V39" t="n">
         <v>199.43</v>
@@ -3265,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>107.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="V40" t="n">
         <v>200.63</v>
@@ -3296,49 +3296,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>3009</v>
+        <v>2812</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3009</v>
+        <v>2812</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="V41" t="n">
-        <v>164.85</v>
+        <v>163.65</v>
       </c>
     </row>
     <row r="42">
@@ -3366,49 +3366,49 @@
         <v>110.93</v>
       </c>
       <c r="H42" t="n">
-        <v>5012</v>
+        <v>4815</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>5012</v>
+        <v>4815</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>96.2</v>
+        <v>99.5</v>
       </c>
       <c r="V42" t="n">
-        <v>129.07</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="43">
@@ -3436,49 +3436,49 @@
         <v>73.95</v>
       </c>
       <c r="H43" t="n">
-        <v>1508</v>
+        <v>1410</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>73.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1508</v>
+        <v>1410</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>73.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>42.3</v>
+        <v>39.5</v>
       </c>
       <c r="V43" t="n">
-        <v>166.05</v>
+        <v>164.85</v>
       </c>
     </row>
     <row r="44">
@@ -3506,49 +3506,49 @@
         <v>108.53</v>
       </c>
       <c r="H44" t="n">
-        <v>8012</v>
+        <v>7563</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>143.12</v>
+        <v>109.73</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.25</v>
+        <v>2.54</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>7760</v>
+        <v>7563</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>108.53</v>
+        <v>109.73</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>67.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="V44" t="n">
-        <v>131.47</v>
+        <v>130.27</v>
       </c>
     </row>
     <row r="45">
@@ -3576,49 +3576,49 @@
         <v>146.71</v>
       </c>
       <c r="H45" t="n">
-        <v>15015</v>
+        <v>14818</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>146.71</v>
+        <v>147.91</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>15015</v>
+        <v>14818</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>146.71</v>
+        <v>147.91</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>105.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V45" t="n">
-        <v>153.29</v>
+        <v>152.09</v>
       </c>
     </row>
     <row r="46">
@@ -3685,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>139.2</v>
+        <v>156.8</v>
       </c>
       <c r="V46" t="n">
         <v>292.81</v>
@@ -3755,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>49</v>
+        <v>45.3</v>
       </c>
       <c r="V47" t="n">
         <v>260.63</v>
@@ -3825,7 +3825,7 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>114.4</v>
+        <v>98.2</v>
       </c>
       <c r="V48" t="n">
         <v>260.63</v>
@@ -3856,49 +3856,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>3761</v>
+        <v>3312</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>109.73</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.18</v>
+        <v>5.61</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3509</v>
+        <v>3312</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>42.6</v>
+        <v>38.9</v>
       </c>
       <c r="V49" t="n">
-        <v>224.85</v>
+        <v>223.65</v>
       </c>
     </row>
     <row r="50">
@@ -3926,49 +3926,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>6261</v>
+        <v>5813</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>109.73</v>
+        <v>77.55</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.18</v>
+        <v>3.28</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>6010</v>
+        <v>5813</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>58</v>
+        <v>65.2</v>
       </c>
       <c r="V50" t="n">
-        <v>223.65</v>
+        <v>222.45</v>
       </c>
     </row>
     <row r="51">
@@ -3996,49 +3996,49 @@
         <v>77.55</v>
       </c>
       <c r="H51" t="n">
-        <v>20013</v>
+        <v>19564</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>112.13</v>
+        <v>78.75</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.28</v>
+        <v>1</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>19761</v>
+        <v>19564</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>77.55</v>
+        <v>78.75</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>181.2</v>
+        <v>169.8</v>
       </c>
       <c r="V51" t="n">
-        <v>222.45</v>
+        <v>221.25</v>
       </c>
     </row>
     <row r="52">
@@ -4066,49 +4066,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>5009</v>
+        <v>4065</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>5009</v>
+        <v>4065</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>54.2</v>
+        <v>59.4</v>
       </c>
       <c r="V52" t="n">
-        <v>224.85</v>
+        <v>223.65</v>
       </c>
     </row>
     <row r="53">
@@ -4136,49 +4136,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>20009</v>
+        <v>16077</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>19.65</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>20009</v>
+        <v>16077</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>19.65</v>
       </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>151.6</v>
+        <v>159.9</v>
       </c>
       <c r="V53" t="n">
-        <v>224.85</v>
+        <v>223.65</v>
       </c>
     </row>
     <row r="54">
@@ -4206,49 +4206,49 @@
         <v>40.57</v>
       </c>
       <c r="H54" t="n">
-        <v>2757</v>
+        <v>2560</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2757</v>
+        <v>2560</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>29.2</v>
+        <v>36.5</v>
       </c>
       <c r="V54" t="n">
-        <v>259.43</v>
+        <v>258.23</v>
       </c>
     </row>
     <row r="55">
@@ -4276,49 +4276,49 @@
         <v>41.77</v>
       </c>
       <c r="H55" t="n">
-        <v>4758</v>
+        <v>4561</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4758</v>
+        <v>4561</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
       <c r="V55" t="n">
-        <v>258.23</v>
+        <v>257.03</v>
       </c>
     </row>
     <row r="56">
@@ -4346,49 +4346,49 @@
         <v>42.97</v>
       </c>
       <c r="H56" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
       <c r="R56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>137.7</v>
+        <v>127.7</v>
       </c>
       <c r="V56" t="n">
-        <v>257.03</v>
+        <v>255.84</v>
       </c>
     </row>
     <row r="57">
@@ -4416,49 +4416,49 @@
         <v>39.37</v>
       </c>
       <c r="H57" t="n">
-        <v>1256</v>
+        <v>1059</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1256</v>
+        <v>1059</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
       <c r="V57" t="n">
-        <v>260.63</v>
+        <v>259.43</v>
       </c>
     </row>
     <row r="58">
@@ -4486,49 +4486,49 @@
         <v>40.57</v>
       </c>
       <c r="H58" t="n">
-        <v>2257</v>
+        <v>2060</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2257</v>
+        <v>2060</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
       <c r="R58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>37.9</v>
+        <v>32</v>
       </c>
       <c r="V58" t="n">
-        <v>259.43</v>
+        <v>258.23</v>
       </c>
     </row>
     <row r="59">
@@ -4556,49 +4556,49 @@
         <v>41.77</v>
       </c>
       <c r="H59" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>76.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="V59" t="n">
-        <v>258.23</v>
+        <v>257.03</v>
       </c>
     </row>
     <row r="60">
@@ -4665,7 +4665,7 @@
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>82.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="V60" t="n">
         <v>259.43</v>
@@ -4696,7 +4696,7 @@
         <v>40.57</v>
       </c>
       <c r="H61" t="n">
-        <v>37757</v>
+        <v>31508</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -4705,13 +4705,13 @@
         <v>40.57</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>16.55</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>37757</v>
+        <v>31508</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -4720,22 +4720,22 @@
         <v>40.57</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>16.55</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>151.8</v>
+        <v>146.8</v>
       </c>
       <c r="V61" t="n">
         <v>259.43</v>
@@ -4805,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>123</v>
+        <v>103.6</v>
       </c>
       <c r="V62" t="n">
         <v>260.63</v>
@@ -4836,49 +4836,49 @@
         <v>110.93</v>
       </c>
       <c r="H63" t="n">
-        <v>7012</v>
+        <v>6815</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>7012</v>
+        <v>6815</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>59.5</v>
+        <v>51.2</v>
       </c>
       <c r="V63" t="n">
-        <v>189.07</v>
+        <v>187.87</v>
       </c>
     </row>
     <row r="64">
@@ -4906,49 +4906,49 @@
         <v>218.27</v>
       </c>
       <c r="H64" t="n">
-        <v>29021</v>
+        <v>28824</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>218.27</v>
+        <v>219.47</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>29021</v>
+        <v>28824</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>218.27</v>
+        <v>219.47</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>151.8</v>
+        <v>136.3</v>
       </c>
       <c r="V64" t="n">
-        <v>81.73</v>
+        <v>80.53</v>
       </c>
     </row>
     <row r="65">
@@ -4976,49 +4976,49 @@
         <v>182.49</v>
       </c>
       <c r="H65" t="n">
-        <v>8018</v>
+        <v>7920</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>182.49</v>
+        <v>183.69</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>8018</v>
+        <v>7920</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>182.49</v>
+        <v>183.69</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>58.9</v>
+        <v>54.7</v>
       </c>
       <c r="V65" t="n">
-        <v>117.51</v>
+        <v>116.31</v>
       </c>
     </row>
     <row r="66">
@@ -5046,49 +5046,49 @@
         <v>141.92</v>
       </c>
       <c r="H66" t="n">
-        <v>7761</v>
+        <v>7663</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>141.92</v>
+        <v>143.12</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>7761</v>
+        <v>7663</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>141.92</v>
+        <v>143.12</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
       <c r="R66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>72.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="V66" t="n">
-        <v>158.08</v>
+        <v>156.88</v>
       </c>
     </row>
     <row r="67">
@@ -5116,49 +5116,49 @@
         <v>7.19</v>
       </c>
       <c r="H67" t="n">
-        <v>10006</v>
+        <v>7817</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>7.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>21.88</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>10006</v>
+        <v>7817</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>7.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>21.88</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
       <c r="R67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>89.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="V67" t="n">
-        <v>292.81</v>
+        <v>291.61</v>
       </c>
     </row>
     <row r="68">
@@ -5186,7 +5186,7 @@
         <v>7.19</v>
       </c>
       <c r="H68" t="n">
-        <v>36006</v>
+        <v>29757</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -5195,13 +5195,13 @@
         <v>7.19</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>17.36</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>36006</v>
+        <v>29757</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -5210,22 +5210,22 @@
         <v>7.19</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>17.36</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>162.1</v>
+        <v>133.8</v>
       </c>
       <c r="V68" t="n">
         <v>292.81</v>
@@ -5256,49 +5256,49 @@
         <v>39.37</v>
       </c>
       <c r="H69" t="n">
-        <v>6006</v>
+        <v>4066</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>6006</v>
+        <v>4066</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
       <c r="R69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>62.9</v>
+        <v>64.3</v>
       </c>
       <c r="V69" t="n">
-        <v>260.63</v>
+        <v>259.43</v>
       </c>
     </row>
     <row r="70">
@@ -5365,7 +5365,7 @@
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>87.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="V70" t="n">
         <v>260.63</v>
@@ -5396,49 +5396,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>4759</v>
+        <v>4562</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4759</v>
+        <v>4562</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>38.6</v>
+        <v>57.2</v>
       </c>
       <c r="V71" t="n">
-        <v>224.85</v>
+        <v>223.65</v>
       </c>
     </row>
     <row r="72">
@@ -5466,49 +5466,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>73</v>
+        <v>96.8</v>
       </c>
       <c r="V72" t="n">
-        <v>223.65</v>
+        <v>222.45</v>
       </c>
     </row>
     <row r="73">
@@ -5536,49 +5536,49 @@
         <v>78.75</v>
       </c>
       <c r="H73" t="n">
-        <v>39762</v>
+        <v>39565</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>78.75</v>
+        <v>79.94</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>39762</v>
+        <v>39565</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>78.75</v>
+        <v>79.94</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>140.9</v>
+        <v>159</v>
       </c>
       <c r="V73" t="n">
-        <v>221.25</v>
+        <v>220.06</v>
       </c>
     </row>
     <row r="74">
@@ -5676,7 +5676,7 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>40009</v>
+        <v>32010</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -5685,13 +5685,13 @@
         <v>75.15000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>19.99</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>40009</v>
+        <v>32010</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -5700,22 +5700,22 @@
         <v>75.15000000000001</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>19.99</v>
       </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>129.3</v>
+        <v>130.7</v>
       </c>
       <c r="V75" t="n">
         <v>224.85</v>
@@ -5746,49 +5746,49 @@
         <v>40.57</v>
       </c>
       <c r="H76" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="V76" t="n">
-        <v>259.43</v>
+        <v>258.23</v>
       </c>
     </row>
     <row r="77">
@@ -5816,49 +5816,49 @@
         <v>41.77</v>
       </c>
       <c r="H77" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>66.2</v>
+        <v>67.3</v>
       </c>
       <c r="V77" t="n">
-        <v>258.23</v>
+        <v>257.03</v>
       </c>
     </row>
     <row r="78">
@@ -5886,49 +5886,49 @@
         <v>44.16</v>
       </c>
       <c r="H78" t="n">
-        <v>31760</v>
+        <v>31563</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>44.16</v>
+        <v>45.36</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>31760</v>
+        <v>31563</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>44.16</v>
+        <v>45.36</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>204.9</v>
+        <v>157.7</v>
       </c>
       <c r="V78" t="n">
-        <v>255.84</v>
+        <v>254.64</v>
       </c>
     </row>
     <row r="79">
@@ -5956,49 +5956,49 @@
         <v>39.37</v>
       </c>
       <c r="H79" t="n">
-        <v>1756</v>
+        <v>1559</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>11.22</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>1756</v>
+        <v>1559</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>11.22</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>28.5</v>
+        <v>87</v>
       </c>
       <c r="V79" t="n">
-        <v>260.63</v>
+        <v>259.43</v>
       </c>
     </row>
     <row r="80">
@@ -6026,49 +6026,49 @@
         <v>40.57</v>
       </c>
       <c r="H80" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>42.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="V80" t="n">
-        <v>259.43</v>
+        <v>258.23</v>
       </c>
     </row>
     <row r="81">
@@ -6096,49 +6096,49 @@
         <v>42.97</v>
       </c>
       <c r="H81" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q81" t="b">
         <v>0</v>
       </c>
       <c r="R81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>77.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V81" t="n">
-        <v>257.03</v>
+        <v>255.84</v>
       </c>
     </row>
     <row r="82">
@@ -6166,49 +6166,49 @@
         <v>40.57</v>
       </c>
       <c r="H82" t="n">
-        <v>21507</v>
+        <v>17575</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>18.28</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>21507</v>
+        <v>17575</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>18.28</v>
       </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" t="n">
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>116.6</v>
+        <v>142.4</v>
       </c>
       <c r="V82" t="n">
-        <v>259.43</v>
+        <v>258.23</v>
       </c>
     </row>
     <row r="83">
@@ -6275,7 +6275,7 @@
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>86.09999999999999</v>
+        <v>101.7</v>
       </c>
       <c r="V83" t="n">
         <v>260.63</v>
@@ -6306,49 +6306,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>3009</v>
+        <v>2812</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3009</v>
+        <v>2812</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>36.6</v>
+        <v>41.7</v>
       </c>
       <c r="V84" t="n">
-        <v>224.85</v>
+        <v>223.65</v>
       </c>
     </row>
     <row r="85">
@@ -6376,49 +6376,49 @@
         <v>110.93</v>
       </c>
       <c r="H85" t="n">
-        <v>5012</v>
+        <v>4815</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>5012</v>
+        <v>4815</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
       <c r="R85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>78</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="V85" t="n">
-        <v>189.07</v>
+        <v>187.87</v>
       </c>
     </row>
     <row r="86">
@@ -6446,49 +6446,49 @@
         <v>73.95</v>
       </c>
       <c r="H86" t="n">
-        <v>1508</v>
+        <v>1410</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>73.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1508</v>
+        <v>1410</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>73.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
         <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>35.2</v>
+        <v>33.3</v>
       </c>
       <c r="V86" t="n">
-        <v>226.05</v>
+        <v>224.85</v>
       </c>
     </row>
     <row r="87">
@@ -6516,49 +6516,49 @@
         <v>108.53</v>
       </c>
       <c r="H87" t="n">
-        <v>7760</v>
+        <v>7563</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>108.53</v>
+        <v>109.73</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>7760</v>
+        <v>7563</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>108.53</v>
+        <v>109.73</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>53</v>
+        <v>61.1</v>
       </c>
       <c r="V87" t="n">
-        <v>191.47</v>
+        <v>190.27</v>
       </c>
     </row>
     <row r="88">
@@ -6586,49 +6586,49 @@
         <v>146.71</v>
       </c>
       <c r="H88" t="n">
-        <v>15015</v>
+        <v>14818</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>146.71</v>
+        <v>147.91</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>15015</v>
+        <v>14818</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>146.71</v>
+        <v>147.91</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" t="n">
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>77.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V88" t="n">
-        <v>999853.29</v>
+        <v>999852.09</v>
       </c>
     </row>
     <row r="89">
@@ -6656,49 +6656,49 @@
         <v>7.19</v>
       </c>
       <c r="H89" t="n">
-        <v>21006</v>
+        <v>17074</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>7.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>18.72</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>21006</v>
+        <v>17074</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>7.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>18.72</v>
       </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" t="n">
         <v>1</v>
       </c>
       <c r="U89" t="n">
-        <v>120.7</v>
+        <v>138.3</v>
       </c>
       <c r="V89" t="n">
-        <v>999992.8100000001</v>
+        <v>999991.61</v>
       </c>
     </row>
     <row r="90">
@@ -6726,49 +6726,49 @@
         <v>39.37</v>
       </c>
       <c r="H90" t="n">
-        <v>3006</v>
+        <v>2062</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3006</v>
+        <v>2062</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
       <c r="R90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" t="n">
         <v>1</v>
       </c>
       <c r="U90" t="n">
-        <v>33.6</v>
+        <v>35.4</v>
       </c>
       <c r="V90" t="n">
-        <v>999960.63</v>
+        <v>999959.4300000001</v>
       </c>
     </row>
     <row r="91">
@@ -6835,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>90.3</v>
+        <v>103.9</v>
       </c>
       <c r="V91" t="n">
         <v>999960.63</v>
@@ -6866,49 +6866,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H92" t="n">
-        <v>3761</v>
+        <v>3312</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>109.73</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K92" t="n">
-        <v>-7.18</v>
+        <v>5.61</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3509</v>
+        <v>3312</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>39.1</v>
+        <v>38</v>
       </c>
       <c r="V92" t="n">
-        <v>999924.85</v>
+        <v>999923.65</v>
       </c>
     </row>
     <row r="93">
@@ -6936,49 +6936,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>6010</v>
+        <v>5813</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>6010</v>
+        <v>5813</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
       <c r="R93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" t="n">
         <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>65.7</v>
+        <v>61.3</v>
       </c>
       <c r="V93" t="n">
-        <v>999923.65</v>
+        <v>999922.45</v>
       </c>
     </row>
     <row r="94">
@@ -7006,49 +7006,49 @@
         <v>77.55</v>
       </c>
       <c r="H94" t="n">
-        <v>20013</v>
+        <v>19564</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>112.13</v>
+        <v>78.75</v>
       </c>
       <c r="K94" t="n">
-        <v>-1.28</v>
+        <v>1</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>19761</v>
+        <v>19564</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>77.55</v>
+        <v>78.75</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" t="b">
         <v>0</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" t="n">
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>161.4</v>
+        <v>188.7</v>
       </c>
       <c r="V94" t="n">
-        <v>999922.45</v>
+        <v>999921.25</v>
       </c>
     </row>
     <row r="95">
@@ -7076,49 +7076,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>5009</v>
+        <v>4065</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>5009</v>
+        <v>4065</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" t="n">
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>44.4</v>
+        <v>54.8</v>
       </c>
       <c r="V95" t="n">
-        <v>999924.85</v>
+        <v>999923.65</v>
       </c>
     </row>
     <row r="96">
@@ -7185,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>132.2</v>
+        <v>167.8</v>
       </c>
       <c r="V96" t="n">
         <v>999924.85</v>
@@ -7216,49 +7216,49 @@
         <v>40.57</v>
       </c>
       <c r="H97" t="n">
-        <v>2757</v>
+        <v>2560</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>2757</v>
+        <v>2560</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="Q97" t="b">
         <v>0</v>
       </c>
       <c r="R97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>32.5</v>
+        <v>37.5</v>
       </c>
       <c r="V97" t="n">
-        <v>999959.4300000001</v>
+        <v>999958.23</v>
       </c>
     </row>
     <row r="98">
@@ -7286,49 +7286,49 @@
         <v>41.77</v>
       </c>
       <c r="H98" t="n">
-        <v>4758</v>
+        <v>4561</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4758</v>
+        <v>4561</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" t="n">
         <v>1</v>
       </c>
       <c r="U98" t="n">
-        <v>41.8</v>
+        <v>46.8</v>
       </c>
       <c r="V98" t="n">
-        <v>999958.23</v>
+        <v>999957.03</v>
       </c>
     </row>
     <row r="99">
@@ -7356,49 +7356,49 @@
         <v>42.97</v>
       </c>
       <c r="H99" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" t="n">
         <v>1</v>
       </c>
       <c r="U99" t="n">
-        <v>109</v>
+        <v>134.4</v>
       </c>
       <c r="V99" t="n">
-        <v>999957.03</v>
+        <v>999955.84</v>
       </c>
     </row>
     <row r="100">
@@ -7426,49 +7426,49 @@
         <v>39.37</v>
       </c>
       <c r="H100" t="n">
-        <v>1256</v>
+        <v>1059</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>1256</v>
+        <v>1059</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>23.5</v>
+        <v>28.5</v>
       </c>
       <c r="V100" t="n">
-        <v>999960.63</v>
+        <v>999959.4300000001</v>
       </c>
     </row>
     <row r="101">
@@ -7496,49 +7496,49 @@
         <v>40.57</v>
       </c>
       <c r="H101" t="n">
-        <v>2257</v>
+        <v>2060</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>2257</v>
+        <v>2060</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" t="n">
         <v>1</v>
       </c>
       <c r="U101" t="n">
-        <v>33.1</v>
+        <v>39.3</v>
       </c>
       <c r="V101" t="n">
-        <v>999959.4300000001</v>
+        <v>999958.23</v>
       </c>
     </row>
     <row r="102">
@@ -7566,49 +7566,49 @@
         <v>41.77</v>
       </c>
       <c r="H102" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
       <c r="R102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102" t="n">
         <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>65.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V102" t="n">
-        <v>999958.23</v>
+        <v>999957.03</v>
       </c>
     </row>
     <row r="103">
@@ -7675,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>68.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="V103" t="n">
         <v>999959.4300000001</v>
@@ -7745,7 +7745,7 @@
         <v>1</v>
       </c>
       <c r="U104" t="n">
-        <v>121.9</v>
+        <v>156.5</v>
       </c>
       <c r="V104" t="n">
         <v>999959.4300000001</v>
@@ -7815,7 +7815,7 @@
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>96.5</v>
+        <v>106.9</v>
       </c>
       <c r="V105" t="n">
         <v>999960.63</v>
@@ -7846,49 +7846,49 @@
         <v>110.93</v>
       </c>
       <c r="H106" t="n">
-        <v>7264</v>
+        <v>6815</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
-        <v>145.51</v>
+        <v>112.13</v>
       </c>
       <c r="K106" t="n">
-        <v>-3.59</v>
+        <v>2.81</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>7012</v>
+        <v>6815</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
       <c r="R106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" t="n">
         <v>1</v>
       </c>
       <c r="U106" t="n">
-        <v>47.6</v>
+        <v>59.6</v>
       </c>
       <c r="V106" t="n">
-        <v>999889.0699999999</v>
+        <v>999887.87</v>
       </c>
     </row>
     <row r="107">
@@ -7916,49 +7916,49 @@
         <v>218.27</v>
       </c>
       <c r="H107" t="n">
-        <v>29273</v>
+        <v>28824</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
-        <v>252.85</v>
+        <v>219.47</v>
       </c>
       <c r="K107" t="n">
-        <v>-0.87</v>
+        <v>0.68</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>29021</v>
+        <v>28824</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>218.27</v>
+        <v>219.47</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
       <c r="R107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" t="n">
         <v>1</v>
       </c>
       <c r="U107" t="n">
-        <v>115.1</v>
+        <v>182</v>
       </c>
       <c r="V107" t="n">
-        <v>999781.73</v>
+        <v>999780.53</v>
       </c>
     </row>
     <row r="108">
@@ -7986,49 +7986,49 @@
         <v>182.49</v>
       </c>
       <c r="H108" t="n">
-        <v>8018</v>
+        <v>7920</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
-        <v>182.49</v>
+        <v>183.69</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>8018</v>
+        <v>7920</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>182.49</v>
+        <v>183.69</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q108" t="b">
         <v>0</v>
       </c>
       <c r="R108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" t="n">
         <v>1</v>
       </c>
       <c r="U108" t="n">
-        <v>53.9</v>
+        <v>63.4</v>
       </c>
       <c r="V108" t="n">
-        <v>999817.51</v>
+        <v>999816.3100000001</v>
       </c>
     </row>
     <row r="109">
@@ -8056,49 +8056,49 @@
         <v>141.92</v>
       </c>
       <c r="H109" t="n">
-        <v>7761</v>
+        <v>7663</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
-        <v>141.92</v>
+        <v>143.12</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>7761</v>
+        <v>7663</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>141.92</v>
+        <v>143.12</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
       <c r="R109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" t="n">
         <v>1</v>
       </c>
       <c r="U109" t="n">
-        <v>63.6</v>
+        <v>77.2</v>
       </c>
       <c r="V109" t="n">
-        <v>999858.08</v>
+        <v>999856.88</v>
       </c>
     </row>
     <row r="110">
@@ -8165,7 +8165,7 @@
         <v>1</v>
       </c>
       <c r="U110" t="n">
-        <v>72.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V110" t="n">
         <v>999992.8100000001</v>
@@ -8196,7 +8196,7 @@
         <v>7.19</v>
       </c>
       <c r="H111" t="n">
-        <v>36006</v>
+        <v>29757</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -8205,13 +8205,13 @@
         <v>7.19</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>17.36</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>36006</v>
+        <v>29757</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
@@ -8220,22 +8220,22 @@
         <v>7.19</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>17.36</v>
       </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
       <c r="R111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" t="n">
         <v>1</v>
       </c>
       <c r="U111" t="n">
-        <v>117.1</v>
+        <v>152.5</v>
       </c>
       <c r="V111" t="n">
         <v>999992.8100000001</v>
@@ -8305,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="U112" t="n">
-        <v>54.6</v>
+        <v>55.3</v>
       </c>
       <c r="V112" t="n">
         <v>999960.63</v>
@@ -8375,7 +8375,7 @@
         <v>1</v>
       </c>
       <c r="U113" t="n">
-        <v>97.5</v>
+        <v>100.6</v>
       </c>
       <c r="V113" t="n">
         <v>999960.63</v>
@@ -8406,49 +8406,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>5011</v>
+        <v>4562</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
-        <v>109.73</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K114" t="n">
-        <v>-5.3</v>
+        <v>4.14</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>4759</v>
+        <v>4562</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q114" t="b">
         <v>0</v>
       </c>
       <c r="R114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114" t="n">
         <v>1</v>
       </c>
       <c r="U114" t="n">
-        <v>42</v>
+        <v>48.4</v>
       </c>
       <c r="V114" t="n">
-        <v>999924.85</v>
+        <v>999923.65</v>
       </c>
     </row>
     <row r="115">
@@ -8476,49 +8476,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H115" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
       <c r="R115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" t="n">
         <v>1</v>
       </c>
       <c r="U115" t="n">
-        <v>72.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V115" t="n">
-        <v>999923.65</v>
+        <v>999922.45</v>
       </c>
     </row>
     <row r="116">
@@ -8546,49 +8546,49 @@
         <v>78.75</v>
       </c>
       <c r="H116" t="n">
-        <v>39762</v>
+        <v>39565</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>78.75</v>
+        <v>79.94</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>39762</v>
+        <v>39565</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>78.75</v>
+        <v>79.94</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q116" t="b">
         <v>0</v>
       </c>
       <c r="R116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
         <v>1</v>
       </c>
       <c r="U116" t="n">
-        <v>134.6</v>
+        <v>178.1</v>
       </c>
       <c r="V116" t="n">
-        <v>999921.25</v>
+        <v>999920.0600000001</v>
       </c>
     </row>
     <row r="117">
@@ -8616,49 +8616,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H117" t="n">
-        <v>10009</v>
+        <v>8069</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>19.38</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>10009</v>
+        <v>8069</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>19.38</v>
       </c>
       <c r="Q117" t="b">
         <v>0</v>
       </c>
       <c r="R117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" t="n">
         <v>1</v>
       </c>
       <c r="U117" t="n">
-        <v>77</v>
+        <v>74.5</v>
       </c>
       <c r="V117" t="n">
-        <v>999924.85</v>
+        <v>999923.65</v>
       </c>
     </row>
     <row r="118">
@@ -8686,7 +8686,7 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>40009</v>
+        <v>32010</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -8695,13 +8695,13 @@
         <v>75.15000000000001</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>19.99</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>40009</v>
+        <v>32010</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
@@ -8710,22 +8710,22 @@
         <v>75.15000000000001</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>19.99</v>
       </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
       <c r="R118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" t="n">
         <v>1</v>
       </c>
       <c r="U118" t="n">
-        <v>131.2</v>
+        <v>165.2</v>
       </c>
       <c r="V118" t="n">
         <v>999924.85</v>
@@ -8756,49 +8756,49 @@
         <v>40.57</v>
       </c>
       <c r="H119" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
       <c r="R119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" t="n">
         <v>1</v>
       </c>
       <c r="U119" t="n">
-        <v>37.2</v>
+        <v>41.3</v>
       </c>
       <c r="V119" t="n">
-        <v>999959.4300000001</v>
+        <v>999958.23</v>
       </c>
     </row>
     <row r="120">
@@ -8826,49 +8826,49 @@
         <v>41.77</v>
       </c>
       <c r="H120" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>7758</v>
+        <v>7561</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
       <c r="R120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" t="n">
         <v>1</v>
       </c>
       <c r="U120" t="n">
-        <v>61.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="V120" t="n">
-        <v>999958.23</v>
+        <v>999957.03</v>
       </c>
     </row>
     <row r="121">
@@ -8896,49 +8896,49 @@
         <v>44.16</v>
       </c>
       <c r="H121" t="n">
-        <v>31760</v>
+        <v>31563</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>44.16</v>
+        <v>45.36</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>31760</v>
+        <v>31563</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>44.16</v>
+        <v>45.36</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="Q121" t="b">
         <v>0</v>
       </c>
       <c r="R121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T121" t="n">
         <v>1</v>
       </c>
       <c r="U121" t="n">
-        <v>109.9</v>
+        <v>144.1</v>
       </c>
       <c r="V121" t="n">
-        <v>999955.84</v>
+        <v>999954.64</v>
       </c>
     </row>
     <row r="122">
@@ -8966,49 +8966,49 @@
         <v>39.37</v>
       </c>
       <c r="H122" t="n">
-        <v>1756</v>
+        <v>1559</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>11.22</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>1756</v>
+        <v>1559</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>11.22</v>
       </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
       <c r="R122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T122" t="n">
         <v>1</v>
       </c>
       <c r="U122" t="n">
-        <v>28.6</v>
+        <v>43.3</v>
       </c>
       <c r="V122" t="n">
-        <v>999960.63</v>
+        <v>999959.4300000001</v>
       </c>
     </row>
     <row r="123">
@@ -9036,49 +9036,49 @@
         <v>40.57</v>
       </c>
       <c r="H123" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3757</v>
+        <v>3560</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
       <c r="R123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123" t="n">
         <v>1</v>
       </c>
       <c r="U123" t="n">
-        <v>40.1</v>
+        <v>49.4</v>
       </c>
       <c r="V123" t="n">
-        <v>999959.4300000001</v>
+        <v>999958.23</v>
       </c>
     </row>
     <row r="124">
@@ -9106,49 +9106,49 @@
         <v>42.97</v>
       </c>
       <c r="H124" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>15759</v>
+        <v>15562</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>42.97</v>
+        <v>44.16</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
       <c r="R124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124" t="n">
         <v>1</v>
       </c>
       <c r="U124" t="n">
-        <v>75.90000000000001</v>
+        <v>113.8</v>
       </c>
       <c r="V124" t="n">
-        <v>999957.03</v>
+        <v>999955.84</v>
       </c>
     </row>
     <row r="125">
@@ -9176,49 +9176,49 @@
         <v>40.57</v>
       </c>
       <c r="H125" t="n">
-        <v>21507</v>
+        <v>17575</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>18.28</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>21507</v>
+        <v>17575</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>18.28</v>
       </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
       <c r="R125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" t="n">
         <v>1</v>
       </c>
       <c r="U125" t="n">
-        <v>116.8</v>
+        <v>150.3</v>
       </c>
       <c r="V125" t="n">
-        <v>999959.4300000001</v>
+        <v>999958.23</v>
       </c>
     </row>
     <row r="126">
@@ -9285,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="U126" t="n">
-        <v>83.7</v>
+        <v>104.3</v>
       </c>
       <c r="V126" t="n">
         <v>999960.63</v>
@@ -9316,49 +9316,49 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>3009</v>
+        <v>2812</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3009</v>
+        <v>2812</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
       <c r="R127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" t="n">
         <v>1</v>
       </c>
       <c r="U127" t="n">
-        <v>35.7</v>
+        <v>44.6</v>
       </c>
       <c r="V127" t="n">
-        <v>999924.85</v>
+        <v>999923.65</v>
       </c>
     </row>
     <row r="128">
@@ -9386,49 +9386,49 @@
         <v>110.93</v>
       </c>
       <c r="H128" t="n">
-        <v>5012</v>
+        <v>4815</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>5012</v>
+        <v>4815</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>110.93</v>
+        <v>112.13</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
       <c r="R128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" t="n">
         <v>1</v>
       </c>
       <c r="U128" t="n">
-        <v>81.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="V128" t="n">
-        <v>999889.0699999999</v>
+        <v>999887.87</v>
       </c>
     </row>
     <row r="129">
@@ -9456,49 +9456,49 @@
         <v>73.95</v>
       </c>
       <c r="H129" t="n">
-        <v>1508</v>
+        <v>1410</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>73.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>1508</v>
+        <v>1410</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>73.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
       <c r="R129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" t="n">
         <v>1</v>
       </c>
       <c r="U129" t="n">
-        <v>33.6</v>
+        <v>44.4</v>
       </c>
       <c r="V129" t="n">
-        <v>999926.05</v>
+        <v>999924.85</v>
       </c>
     </row>
     <row r="130">
@@ -9526,49 +9526,49 @@
         <v>108.53</v>
       </c>
       <c r="H130" t="n">
-        <v>7760</v>
+        <v>7563</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>108.53</v>
+        <v>109.73</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>7760</v>
+        <v>7563</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130" t="n">
-        <v>108.53</v>
+        <v>109.73</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
       <c r="R130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T130" t="n">
         <v>1</v>
       </c>
       <c r="U130" t="n">
-        <v>52.6</v>
+        <v>62.8</v>
       </c>
       <c r="V130" t="n">
-        <v>999891.47</v>
+        <v>999890.27</v>
       </c>
     </row>
   </sheetData>
@@ -9635,22 +9635,22 @@
         <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7</v>
+        <v>10.97</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5.94</v>
+        <v>10.97</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>174.77</v>
+        <v>173.91</v>
       </c>
     </row>
     <row r="3">
@@ -9661,22 +9661,22 @@
         <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>4.27</v>
+        <v>10.93</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>4.56</v>
+        <v>10.93</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>234.77</v>
+        <v>233.88</v>
       </c>
     </row>
     <row r="4">
@@ -9687,22 +9687,22 @@
         <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>4.61</v>
+        <v>10.91</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5.03</v>
+        <v>10.91</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>999934.77</v>
+        <v>999933.88</v>
       </c>
     </row>
   </sheetData>
